--- a/corrected-bank-specimens-for-user/12-lordship-9035-q1-2026/parsed-excel/LIBcashbk2 2026 1qtr - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/12-lordship-9035-q1-2026/parsed-excel/LIBcashbk2 2026 1qtr - parsed.xlsx
@@ -428,7 +428,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-08T16:17:01.637Z</v>
+        <v>2026-07-14T13:50:04.424Z</v>
       </c>
     </row>
     <row r="5">

--- a/corrected-bank-specimens-for-user/12-lordship-9035-q1-2026/parsed-excel/LIBcashbk2 2026 1qtr - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/12-lordship-9035-q1-2026/parsed-excel/LIBcashbk2 2026 1qtr - parsed.xlsx
@@ -428,7 +428,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-14T13:50:04.424Z</v>
+        <v>2026-07-17T19:29:58.191Z</v>
       </c>
     </row>
     <row r="5">
